--- a/projects/QNL/sources/QNL_Assets_Location_Relationships.xlsx
+++ b/projects/QNL/sources/QNL_Assets_Location_Relationships.xlsx
@@ -12,6 +12,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAV" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAV" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FCU" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DX" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EF" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEF" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCU" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TEF" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HEX" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KEF" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHW" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ELEC" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHWPU" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
@@ -21,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,8 +57,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -66,8 +84,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -90,11 +113,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -103,6 +140,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -572,6 +613,757 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Room Tag</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Feeds</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>CCU_B01</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_048_QTEL_ROOM</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>REST TOOM (MEN) B.061</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>CCU_B02</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_048_QTEL_ROOM</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>REST TOOM (MEN) B.061</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>CCU_B03</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_050_TELECOM_ROOM</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>REST TOOM (MEN) B.061</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>CCU_B04</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_050_TELECOM_ROOM</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>REST TOOM (MEN) B.061</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>CCU_B05</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_089_SERVER_ROOM</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>REST TOOM (MEN) B.061</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>CCU_B06</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_089_SERVER_ROOM</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>REST TOOM (MEN) B.061</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>CCU_B07</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_089_SERVER_ROOM</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>REST TOOM (MEN) B.061</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>CCU_B08</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B141_VAU_VAULT</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>REST TOOM (MEN) 141.061</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>CCU_B09</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B141_VAU_VAULT</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>REST TOOM (MEN) 141.061</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>CCU_B10</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_222_IDF</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>REST TOOM (MEN) B.061</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>CCU_B11</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_222_IDF</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>REST TOOM (MEN) B.061</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Room Tag</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Feeds</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>TEF_B02A</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_070_PLANT_ROOM_02</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>RESTROOM (MEN) B.032</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>TEF_B02B</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_070_PLANT_ROOM_02</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>RESTROOM (WOMEN) B.033</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>TEF_B01A</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_110_PLANT_ROOM_03</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>RESTROOM (MEN) B.046</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>TEF_B01B</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_110_PLANT_ROOM_03</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>RESTROOM (WOMEN) B.047</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>TEF_B03A</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_120_COMPACT_SHELVING_-MAIN_COLLECTION</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>VIP RESTROOM B.146</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>TEF_B03B</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_120_COMPACT_SHELVING_-MAIN_COLLECTION</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>VIP RESTROOM B.147</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>TEF_101C</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_L1-E2_ELEC_SHAFT</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>REST TOOM (MEN) L1.061</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>TEF_102C</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_L1-E1_ELEC_SHAFT</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>REST TOOM (WOMEN) L1.025</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Room Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>HEX05</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_211_PH_PLANT_ROOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>HEX01</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_220_PLANT_ROOM_04</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>HEX02</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_220_PLANT_ROOM_04</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>HEX03</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_220_PLANT_ROOM_04</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>HEX04</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_220_PLANT_ROOM_04</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Room Tag</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Feeds</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>KEF_B019</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_049_MEP_KITCHEN</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>MEP KITCHEN B.049</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>KEF_B04</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_001A_BREAK_OUT_AREA</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>KITCHEN B.002</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>KEF_B020</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_052_CORRIDOR_3</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>BINDING AND Reservation Space B.043</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>KEF_101</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_L1_067_RESTAURANT</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>RESTAURANT L1.067</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Room Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>CHW_P01</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_220_PLANT_ROOM_04</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>CHW_P02</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_220_PLANT_ROOM_04</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>CHW_P03</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_220_PLANT_ROOM_04</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>CHW_P04</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_220_PLANT_ROOM_04</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Room Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>ELEC_Gen</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_080_GENERATOR</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Room Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>CHWPU_P01</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_220_PLANT_ROOM_04</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -8758,4 +9550,1018 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Room Tag</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Feeds</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>DX_B11</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B046_ITT_ITTIGATION_CONTROL_ROOM</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B046_ITT_ITTIGATION_CONTROL_ROOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>DX_B01</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_081_MV_ROOM</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_081_MV_ROOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>DX_B02</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_081_MV_ROOM</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_081_MV_ROOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>DX_B03</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_082_TRANSFORMER_ROOM</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_082_TRANSFORMER_ROOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>DX_B04</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_082_TRANSFORMER_ROOM</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_082_TRANSFORMER_ROOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>DX_B14</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_082_TRANSFORMER_ROOM</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_082_TRANSFORMER_ROOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>DX_B08</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_084_UPS_BATTERY_ROOM</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_084_UPS_BATTERY_ROOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>DX_B09</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_084_UPS_BATTERY_ROOM</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_084_UPS_BATTERY_ROOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>DX_B20</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_092_STORAGE</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_092_STORAGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>DX_B13</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_093_TRANSH_CHAMBER</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_093_TRANSH_CHAMBER</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>DX_B15</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_093_TRANSH_CHAMBER</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_093_TRANSH_CHAMBER</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>DX_B07</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_095_EMERGENCY_LIGHTING_BATTERY_ROOM</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_095_EMERGENCY_LIGHTING_BATTERY_ROOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>DX_B16</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_095_EMERGENCY_LIGHTING_BATTERY_ROOM</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_095_EMERGENCY_LIGHTING_BATTERY_ROOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>DX_B10</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_102_SECURITY_&amp;_BMS</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_102_SECURITY_&amp;_BMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>DX_B22</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B106_RES_REST_ROOM_SECURITY</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B106_RES_REST_ROOM_SECURITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>DX_B12</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_107_SECURITY_EQUIPMENT_ROOM</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_107_SECURITY_EQUIPMENT_ROOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>DX_B23</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_107_SECURITY_EQUIPMENT_ROOM</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_107_SECURITY_EQUIPMENT_ROOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>DX_B05</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_083_HV_ROOM</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_083_HV_ROOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>DX_B06</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_083_HV_ROOM</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_083_HV_ROOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>DX_B17</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_045A_REFRIGERATE_STORE</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_045A_REFRIGERATE_STORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>DX_B18</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_045A_REFRIGERATE_STORE</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_045A_REFRIGERATE_STORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>DX_B19</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_045A_REFRIGERATE_STORE</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_045A_REFRIGERATE_STORE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>DX_B21</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_P_004_PLANT_ZONE</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_P_004_PLANT_ZONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>DX_B24</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_P_004_PLANT_ZONE</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_P_004_PLANT_ZONE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Room Tag</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Feeds</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>EF_BBV01</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_070_PLANT_ROOM_02</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>UPS BATERRY ROOM B.084</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>EF_BBV02</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_070_PLANT_ROOM_02</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>UPS BATERRY ROOM B.084</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>EF_B14</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_071_FIRE_COMMAND_ROOM</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Fire Command B.071</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>EF_B13</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_072_SPRIMKLERS_PUMPS_&amp;_ZONES_VALVES</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Sprinklers Pumps B.072</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>EF_B09</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_080_GENERATOR</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Generator B.080</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>EF_B05</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_085_FUMIGATION_ROOM</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>FUMIGATION B.085</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>EF_B11</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_091_FUEL_ROOM</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Fuel pump room B.091</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>EF_B10</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_093_TRANSH_CHAMBER</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Trash room B.093</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>EF_B07</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_109_LOADING_AREA</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Loading Room B.109</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>EF_B08</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_109_LOADING_AREA</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Loading Room B.109</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>EF_B15</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_109_LOADING_AREA</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Loading Room B.109</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>EF_B16</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_109_LOADING_AREA</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Loading Room B.109</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>EF_201</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_L1-L-3_L-3</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>FRONT KITCHEN L1.067</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>EF_RP02</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_P_004_PLANT_ZONE</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Plant Zone P.007</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>EF_B06</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_055_DIGITIZATION_CENTER</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>DIGITIZATION CENTER B.055</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>EF_B12</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_B_214_IDF_ROOM</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Pantry B.144</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>EF_RP01</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_P_002_PLANT_ZONE</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Plant Zone P.002</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>EF_RP03</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_P_007_PLANT_ZONE</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Plant Zone P.004</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Room Tag</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Feeds</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>SEF_RP07</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_P_004_PLANT_ZONE</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>Plant Zone P.004</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>SEF_RP08</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_P_004_PLANT_ZONE</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Plant Zone P.004</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>SEF_RP09</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_P_004_PLANT_ZONE</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Plant Zone P.004</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>SEF_ZoneB</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_P_004_PLANT_ZONE</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>SEF_RP04</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_P_002_PLANT_ZONE</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Plant Zone P.002</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>SEF_RP05</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_P_002_PLANT_ZONE</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Plant Zone P.002</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>SEF_RP06</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_P_002_PLANT_ZONE</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Plant Zone P.002</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>SEF_ZoneA</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_P_002_PLANT_ZONE</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>SEF_RP10</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_P_007_PLANT_ZONE</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Plant Zone P.007</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>SEF_ZoneC</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_P_007_PLANT_ZONE</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>SEF_RP11</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_P_006_PLANT_ZONE</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Plant Zone P.006</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>SEF_RP12</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>entity:QNL_P_006_PLANT_ZONE</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Plant Zone P.006</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>